--- a/api/templates/list_r_resistant_test/vi.xlsx
+++ b/api/templates/list_r_resistant_test/vi.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-18.04\home\nsabaj\Repositories\aspect\api\templates\list_r_resistant_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D2853D6-8049-405D-8C9D-5539D8289067}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F891EC6E-FA5D-4FAF-A500-A929A88E0F78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0E5D046B-46E4-4AC6-B2A8-F60000E7545A}"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{0E5D046B-46E4-4AC6-B2A8-F60000E7545A}"/>
   </bookViews>
   <sheets>
     <sheet name="List-R resistant test" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
   <si>
     <t>&lt;fullName&gt;</t>
   </si>
@@ -134,6 +134,12 @@
   </si>
   <si>
     <t xml:space="preserve"> (ký tên, ghi rõ họ tên)</t>
+  </si>
+  <si>
+    <t>&lt;notes&gt;</t>
+  </si>
+  <si>
+    <t>&lt;States&gt;</t>
   </si>
 </sst>
 </file>
@@ -796,7 +802,9 @@
         <v>16</v>
       </c>
       <c r="B4" s="36"/>
-      <c r="C4" s="37"/>
+      <c r="C4" s="37" t="s">
+        <v>34</v>
+      </c>
       <c r="D4" s="37"/>
       <c r="E4" s="3" t="s">
         <v>18</v>
@@ -897,7 +905,7 @@
         <v>3</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">

--- a/api/templates/list_r_resistant_test/vi.xlsx
+++ b/api/templates/list_r_resistant_test/vi.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-18.04\home\nsabaj\Repositories\aspect\api\templates\list_r_resistant_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F891EC6E-FA5D-4FAF-A500-A929A88E0F78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F22FF6F2-3105-4909-891A-40848F82987D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{0E5D046B-46E4-4AC6-B2A8-F60000E7545A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0E5D046B-46E4-4AC6-B2A8-F60000E7545A}"/>
   </bookViews>
   <sheets>
     <sheet name="List-R resistant test" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>&lt;fullName&gt;</t>
   </si>
@@ -140,6 +140,9 @@
   </si>
   <si>
     <t>&lt;States&gt;</t>
+  </si>
+  <si>
+    <t>&lt;targetGroup&gt;</t>
   </si>
 </sst>
 </file>
@@ -896,7 +899,7 @@
         <v>2</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>7</v>
